--- a/research/honduras/excel/Honduras_price_cost_finance_varieties.xlsx
+++ b/research/honduras/excel/Honduras_price_cost_finance_varieties.xlsx
@@ -1969,30 +1969,90 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Aug 2017</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">national coffee park (plants)</t>
+        </is>
+      </c>
+      <c r="C8" s="9">
+        <v>60</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ web extract, NOT verified</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La Prensa, 25 Aug 2017 (search extract)</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60 % of the national coffee park is improved plants resistant to rust; national seed demand: 65 % Lempira, 25 % Catuaí, 10 % other varieties</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Oct 2017</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">farms sampled by the rust early-warning system</t>
         </is>
       </c>
-      <c r="D8" s="8">
+      <c r="D9" s="8">
         <v>56.08</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">⚠ web extract, NOT verified</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">IHCAFE SAT bulletin No 8 (search snippet)</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Lempira = 56.08 % of sampled farms, 67.74 % of farms classed as susceptible</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~2020</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">national, % of cultivation</t>
+        </is>
+      </c>
+      <c r="C10" s="9">
+        <v>60</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ web extract, NOT verified</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perfect Daily Grind, Mar 2020 (search extract)</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">about 60 % of Honduran coffee is planted with resistant varieties (Lempira, IHCAFE 90, Parainema)</t>
         </is>
       </c>
     </row>

--- a/research/honduras/excel/Honduras_price_cost_finance_varieties.xlsx
+++ b/research/honduras/excel/Honduras_price_cost_finance_varieties.xlsx
@@ -1579,7 +1579,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Still resistant in April 2018 (IHCAFE, 4 new rust strains found); not listed as resistant in USDA 2020 (16 new strains, April 2019)</t>
+          <t xml:space="preserve">Still resistant per IHCAFE in April 2018 (USDA). About 80 % resistance to the new strain (IHCAFE via La Prensa, Aug 2017 ⚠). Not named as resistant by USDA after 2018</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAIN 2013 ("The varieties developed were the IHCAFE 90 and Lempira"); GAIN 2018; GAIN 2020</t>
+          <t xml:space="preserve">GAIN 2013 ("The varieties developed were the IHCAFE 90 and Lempira"); GAIN 2018; La Prensa 2017 (extract)</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Release year not in a document we could open; the name points to 1990.</t>
+          <t xml:space="preserve">Release year: the name points to 1990; not read in an official record.</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistance loss confirmed by IHCAFE in April 2017; rust on 3 % of Lempira plants</t>
+          <t xml:space="preserve">Weakening seen in IHCAFE monitoring from 2007, susceptible by 2015 (PROMECAFE 2019 ⚠); loss confirmed by IHCAFE in April 2017, rust on 3 % of Lempira plants (USDA)</t>
         </is>
       </c>
       <c r="F6" s="12">
@@ -1629,12 +1629,12 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAIN 2017 ("In April 2017, IHCAFE confirmed the loss of resistance of the Lempira variety"; "rust was present on three percent of Lempira variety plants")</t>
+          <t xml:space="preserve">GAIN 2017 ("In April 2017, IHCAFE confirmed the loss of resistance of the Lempira variety"); PROMECAFE 24th symposium 2019 (extract)</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Release 1997/98 and the 56 % share of sampled farms (IHCAFE bulletin No 8, Oct 2017) are search snippets only.</t>
+          <t xml:space="preserve">Release 1997/98 is a web extract.</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Still resistant per IHCAFE (USDA 2018, 2020, 2021); USDA 2025–26: area growth "driven by the introduction of the Parainema variety"</t>
+          <t xml:space="preserve">Called still resistant by IHCAFE in USDA 2018, 2020 and 2021 (last explicit statement: May 2021). Web extracts (⚠): new rust races overcome it in some zones (2019). USDA 2025–26: harvest and area growth from Parainema</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAIN 2014 (third IHCAFE variety listed); GAIN 2018; GAIN 2020; GAIN 2025</t>
+          <t xml:space="preserve">GAIN 2014 (third IHCAFE variety listed); GAIN 2018, 2020, 2021, 2025, 2026</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Release year 2004 is a search snippet.</t>
+          <t xml:space="preserve">Release year 2004 is a web extract.</t>
         </is>
       </c>
     </row>
@@ -1688,12 +1688,12 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 varieties presented by IHCAFE</t>
+          <t xml:space="preserve">bred in Brazil (Icatu, Obatá) and Guatemala (Anacafé 14); validated and released by IHCAFE</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feb 2024</t>
+          <t xml:space="preserve">2024</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presented as rust resistant, productive; seed for at least 1 500 manzanas in 2024</t>
+          <t xml:space="preserve">Presented as rust resistant and productive; seed for at least 1 500 manzanas in 2024</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -1718,14 +1718,14 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search snippet only; first releases about 20 years after Parainema.</t>
+          <t xml:space="preserve">Web extract only; first releases about 20 years after Parainema.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 more in the pipeline</t>
+          <t xml:space="preserve">2 more in release process</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">announced</t>
+          <t xml:space="preserve">2026 (announced)</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">"at least 4 more rust-resistant varieties" being prepared</t>
+          <t xml:space="preserve">"two new varieties in the process of release: rust resistant, drought tolerant, high cup quality"</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">La Prensa, "Ihcafé se prepara para liberar 4 variedades más resistentes a roya"</t>
+          <t xml:space="preserve">web extract, early 2026 (page not identified with certainty); an earlier La Prensa article announced 4, probably including the three of 2024</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search snippet only.</t>
+          <t xml:space="preserve">Web extract only.</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990-2004: 3 releases (IHCAFE 90, Lempira, Parainema). 2005-2023: none. Feb 2024: 3 (Ihcatú 75, Anacafé 14 SHN, Obatá SHN, ⚠). Announced: 4 more (⚠).</t>
+          <t xml:space="preserve">1990-2004: 3 varieties bred by IHCAFE (IHCAFE 90, Lempira, Parainema). 2005-2023: none found. 2024: 3 bred abroad and released by IHCAFE (Ihcatú 75, Anacafé 14 SHN, Obatá SHN, ⚠). 2026: 2 more in release process (⚠).</t>
         </is>
       </c>
     </row>
@@ -2006,6 +2006,9 @@
         <is>
           <t xml:space="preserve">farms sampled by the rust early-warning system</t>
         </is>
+      </c>
+      <c r="C9" s="9">
+        <v>17.2</v>
       </c>
       <c r="D9" s="8">
         <v>56.08</v>

--- a/research/honduras/excel/Honduras_price_cost_finance_varieties.xlsx
+++ b/research/honduras/excel/Honduras_price_cost_finance_varieties.xlsx
@@ -1564,22 +1564,22 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Catimor (Caturra × Timor Hybrid)</t>
+          <t xml:space="preserve">Catimor (Timor Hybrid 832/1 × Caturra)</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990s</t>
+          <t xml:space="preserve">1990</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠ web extract, NOT verified</t>
+          <t xml:space="preserve">✔ document read (ihcafe_docs2)</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Still resistant per IHCAFE in April 2018 (USDA). About 80 % resistance to the new strain (IHCAFE via La Prensa, Aug 2017 ⚠). Not named as resistant by USDA after 2018</t>
+          <t xml:space="preserve">Resistant 1990–2015; from 2016 about 20 % of plants susceptible to the new rust races (IHCAFE, 2019). USDA 2018: still resistant. World Coffee Research: "recently confirmed susceptible in Honduras"</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAIN 2013 ("The varieties developed were the IHCAFE 90 and Lempira"); GAIN 2018; La Prensa 2017 (extract)</t>
+          <t xml:space="preserve">Morales &amp; Grajeda (IHCAFE), PROMECAFE 24th symposium 2019, table "Durabilidad de resistencia"; GAIN 2018; WCR variety page</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Release year: the name points to 1990; not read in an official record.</t>
+          <t xml:space="preserve">Effective resistance 25 years (IHCAFE).</t>
         </is>
       </c>
     </row>
@@ -1611,30 +1611,30 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1997–98</t>
+          <t xml:space="preserve">1998</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠ web extract, NOT verified</t>
+          <t xml:space="preserve">✔ document read (ihcafe_docs2)</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weakening seen in IHCAFE monitoring from 2007, susceptible by 2015 (PROMECAFE 2019 ⚠); loss confirmed by IHCAFE in April 2017, rust on 3 % of Lempira plants (USDA)</t>
+          <t xml:space="preserve">Resistant 1998–2001; tolerant 2002–2015 (rust already on 100 % of plants, low severity, in seed plots in July 2007); susceptible in 2016 (Olancho, full defoliation), spread over the whole country 2017–2019. USDA: IHCAFE confirmed the loss in April 2017</t>
         </is>
       </c>
       <c r="F6" s="12">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAIN 2017 ("In April 2017, IHCAFE confirmed the loss of resistance of the Lempira variety"); PROMECAFE 24th symposium 2019 (extract)</t>
+          <t xml:space="preserve">Morales &amp; Grajeda (IHCAFE), PROMECAFE 2019; GAIN 2017; WCR variety page</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Release 1997/98 is a web extract.</t>
+          <t xml:space="preserve">Effective resistance 17 years (IHCAFE).</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sarchimor T-5296 (Villa Sarchí × Timor Hybrid)</t>
+          <t xml:space="preserve">Sarchimor, selection of T5296</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠ web extract, NOT verified</t>
+          <t xml:space="preserve">✔ document read (ihcafe_docs2)</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Called still resistant by IHCAFE in USDA 2018, 2020 and 2021 (last explicit statement: May 2021). Web extracts (⚠): new rust races overcome it in some zones (2019). USDA 2025–26: harvest and area growth from Parainema</t>
+          <t xml:space="preserve">Resistant 2004–2019 in IHCAFE tests (fully resistant to the new races); USDA 2018, 2020, 2021: still resistant. Nothing later found</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAIN 2014 (third IHCAFE variety listed); GAIN 2018, 2020, 2021, 2025, 2026</t>
+          <t xml:space="preserve">Morales &amp; Grajeda (IHCAFE), PROMECAFE 2019; WCR ("released in 2004"); GAIN 2018, 2020, 2021, 2025</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Release year 2004 is a web extract.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -1688,22 +1688,22 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">bred in Brazil (Icatu, Obatá) and Guatemala (Anacafé 14); validated and released by IHCAFE</t>
+          <t xml:space="preserve">bred abroad (Brazil: Icatu, Obatá by IAC; Guatemala: Anacafé 14), released by IHCAFE</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024</t>
+          <t xml:space="preserve">Feb 2024</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠ web extract, NOT verified</t>
+          <t xml:space="preserve">✔ document read (ihcafe_docs2)</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presented as rust resistant and productive; seed for at least 1 500 manzanas in 2024</t>
+          <t xml:space="preserve">Presented as more rust resistant and productive; seed for at least 1 500 manzanas in 2024. Caution: IHCAFE's 2019 study listed the Icatu 75 line as susceptible since 2016 and Obatá as 20 % susceptible</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -1713,54 +1713,12 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">El Heraldo, "Honduras dispone de tres nuevas variedades de café" (2024)</t>
+          <t xml:space="preserve">El Heraldo, 29 Feb 2024 (read); La Prensa, 29 Sep 2023 (read: "at least 4" to be released in 2024; last release Parainema 2004); PROMECAFE 2019</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Web extract only; first releases about 20 years after Parainema.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 more in release process</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">IHCAFE research centres</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026 (announced)</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⚠ web extract, NOT verified</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"two new varieties in the process of release: rust resistant, drought tolerant, high cup quality"</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">web extract, early 2026 (page not identified with certainty); an earlier La Prensa article announced 4, probably including the three of 2024</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Web extract only.</t>
+          <t xml:space="preserve">First releases 20 years after Parainema.</t>
         </is>
       </c>
     </row>
@@ -1774,14 +1732,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990-2004: 3 varieties bred by IHCAFE (IHCAFE 90, Lempira, Parainema). 2005-2023: none found. 2024: 3 bred abroad and released by IHCAFE (Ihcatú 75, Anacafé 14 SHN, Obatá SHN, ⚠). 2026: 2 more in release process (⚠).</t>
+          <t xml:space="preserve">Releases: IHCAFE 90 (1990), Lempira (1998), Parainema (2004), bred by IHCAFE; none 2005–2023; 29 Feb 2024: Ihcatú 75, Anacafé 14 SHN, Obatá SHN, bred abroad and released by IHCAFE (Sep 2023: at least 4 announced).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yield by variety: no official figure found. Web extract: Obatá about 20 % more productive than Caturra (⚠). PAPP target 5 → 45 qq per manzana (USDA 2017).</t>
+          <t xml:space="preserve">Yield by variety: no official figure found. IHCAFE (2019): the change to resistant varieties raised productivity. PAPP target 5 → 45 qq per manzana (USDA 2017).</t>
         </is>
       </c>
     </row>
@@ -1879,30 +1837,30 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013</t>
+          <t xml:space="preserve">since 2012</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">national, manzanas</t>
+          <t xml:space="preserve">cultivated area, dominated by Lempira</t>
         </is>
       </c>
       <c r="C5" s="9">
-        <v>50</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⚠ web extract, NOT verified</t>
+        <v>65</v>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ document read (ihcafe_docs2)</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">El Heraldo 2013 (search snippet)</t>
+          <t xml:space="preserve">Morales &amp; Grajeda (IHCAFE), PROMECAFE 2019 (read)</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">of 400,000 manzanas cultivated, 200,000 resistant; the rest Catuaí, Caturra, Bourbon, Pacas</t>
+          <t xml:space="preserve">Estos materiales resistentes reemplazaron los susceptibles y constituyen el 65% del área cultivada desde 2012 dominada por Lempira.</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2581,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rust emergency credit (banks, BANHPROVI, BANADESA)</t>
+          <t xml:space="preserve">Rust credit made available (banks, BCH, BANHPROVI, BANADESA, IHCAFE)</t>
         </is>
       </c>
       <c r="D7" s="9">
@@ -2639,27 +2597,27 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">growers hit by rust; BANADESA loans up to L25,000</t>
+          <t xml:space="preserve">L335 M actually used by April 2014; BANADESA loans up to L25,000, banks up to L150,000</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">to be repaid by 2019 (USDA)</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⚠ web extract, NOT verified</t>
+          <t xml:space="preserve">10 % interest, 7 years; to be repaid by 2019 (USDA)</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ document read (ihcafe_docs2)</t>
         </is>
       </c>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">El Heraldo 2013 (search snippet); GAIN 2017 for the 2019 repayment date</t>
+          <t xml:space="preserve">El Heraldo, 7 Apr 2014 (read); GAIN 2017 for the 2019 repayment date</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">approximately 1,715 million lempiras were made available to coffee growers to confront the advance of coffee rust</t>
+          <t xml:space="preserve">se ha puesto a disposición de los caficultores alrededor de 1,715 millones de lempiras ... Del total de estos recursos se han utilizado unos 335 millones de lempiras</t>
         </is>
       </c>
     </row>
@@ -2776,37 +2734,37 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">all registered growers who ask</t>
+          <t xml:space="preserve">all growers who ask</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">L200 per qq produced in 2016/17 (decree, snippet) — USDA wrote "about $25 per 100 pounds"; repaid by US$1.50/qq deducted on exports</t>
+          <t xml:space="preserve">L200 per quintal oro produced in 2016/17 (≈ 8,4 $, not the "25 $" in USDA 2020); up to L1 900 M; repaid by 1,50 $ per qq retained at export</t>
         </is>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">✔ USDA report (read)</t>
+          <t xml:space="preserve">✔ document read (ihcafe_docs2)</t>
         </is>
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAIN 2020 (US$77 million, 5 Sep 2018); decree text via search snippet (L1,900 M, L200/qq)</t>
+          <t xml:space="preserve">El Heraldo, 29 Aug 2018 (read); GAIN 2020 (about 77 M$, 5 Sep 2018)</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">On September 5, 2018, the Honduran Congress authorized IHCAFE to contract ... financing for about $77 million.</t>
+          <t xml:space="preserve">Todos los caficultores que lo soliciten podrán obtener préstamos de 200 lempiras por cada quintal de café oro producido ... hasta 1,900 millones de lempiras ... retendrán 1.50 dólares ... por cada quintal oro</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decreto 47-2018 debt readjustment + BANHPROVI coffee fund</t>
+          <t xml:space="preserve">Fondo para el Sector Cafetero (BANHPROVI)</t>
         </is>
       </c>
       <c r="D11" s="9">
@@ -2814,35 +2772,35 @@
       </c>
       <c r="E11" s="13">
         <f>INDEX(Price_annual!F5:F26,MATCH(A11,Price_annual!A5:A26,0))</f>
-        <v>24.50853891</v>
+        <v>23.90272829</v>
       </c>
       <c r="F11" s="7">
         <f>D11/E11</f>
-        <v>12.240631769264454</v>
+        <v>12.550868518448945</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">&gt; 55,000 growers</t>
+          <t xml:space="preserve">backs refinancing and debt readjustment of growers</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">up to 20 years at 2 %</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⚠ web extract, NOT verified</t>
+          <t xml:space="preserve">L300 M in three instalments</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ document read (ihcafe_docs2)</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">El Heraldo; MiAmbiente (search snippets)</t>
+          <t xml:space="preserve">El Heraldo, 29 Aug 2018 (read)</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">BANHPROVI Coffee Sector Fund L300 million</t>
+          <t xml:space="preserve">El Fondo para el Sector Cafetero ... por la cantidad de 300 millones de lempiras ... para respaldar operaciones de refinanciamiento y readecuación</t>
         </is>
       </c>
     </row>

--- a/research/honduras/excel/Honduras_price_cost_finance_varieties.xlsx
+++ b/research/honduras/excel/Honduras_price_cost_finance_varieties.xlsx
@@ -1579,7 +1579,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resistant 1990–2015; from 2016 about 20 % of plants susceptible to the new rust races (IHCAFE, 2019). USDA 2018: still resistant. World Coffee Research: "recently confirmed susceptible in Honduras"</t>
+          <t xml:space="preserve">Resistant 1990–2015; from 2016 about 20 % of plants susceptible to the new rust races (IHCAFE, 2019); 80 % resistance to the new strain (IHCAFE via La Prensa, 24 Aug 2017). USDA 2018: still resistant. World Coffee Research: "recently confirmed susceptible in Honduras"</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -1927,7 +1927,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aug 2017</t>
+          <t xml:space="preserve">24 Aug 2017</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
@@ -1938,19 +1938,19 @@
       <c r="C8" s="9">
         <v>60</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⚠ web extract, NOT verified</t>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ document read (ihcafe_docs2)</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">La Prensa, 25 Aug 2017 (search extract)</t>
+          <t xml:space="preserve">La Prensa, 24 Aug 2017 (read, ihcafe_docs3)</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">60 % of the national coffee park is improved plants resistant to rust; national seed demand: 65 % Lempira, 25 % Catuaí, 10 % other varieties</t>
+          <t xml:space="preserve">En la actualidad, el 60% del parque cafetalero nacional está conformado por plantas mejoradas y resistentes a la roya y otras enfermedades.</t>
         </is>
       </c>
     </row>
